--- a/upload/iniciativa.xlsx
+++ b/upload/iniciativa.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x6557308\Desktop\Trabalho\CGE - Transparência RD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_0C7444C9A5E6AFB2BCF6ACFBE0382C1F7757FBC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B3AC438-7526-4625-972A-FF0F956A06E2}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Portal Transparência - CGE" sheetId="4" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portal Transparência - CGE'!$A$1:$D$1</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="46">
   <si>
     <t>Código Iniciativa </t>
   </si>
@@ -65,13 +64,6 @@
     <t>X</t>
   </si>
   <si>
-    <t>Fortalecimento do atendimento da rede socioassistencial com execução de um _x000D_
-plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do Centro de Referência de Assistência Social (CRAS) e Centro de Referência _x000D_
-Especializado de Assistência Social (CREAS), contratação de equipe técnica e _x000D_
-aquisição de material de consumo de acordo com detalhamento a ser construído _x000D_
-prioritariamente.</t>
-  </si>
-  <si>
     <t>XII</t>
   </si>
   <si>
@@ -90,58 +82,12 @@
     <t>XIII</t>
   </si>
   <si>
-    <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da _x000D_
-infraestrutura viária.</t>
-  </si>
-  <si>
-    <t>Fortalecimento da política pública de gestão do manejo da fauna silvestre, de _x000D_
-acordo com mapeamento de necessidades a ser detalhado, a partir de ações como _x000D_
-da estruturação e custeio dos serviços prestados pelos Centros de Triagem e Reabilitação de Animais Silvestres (Cetas) que atendam à Bacia Hidrográfica do Rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da fauna.</t>
-  </si>
-  <si>
-    <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio _x000D_
-Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de _x000D_
-acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) _x000D_
-de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de _x000D_
-áreas prioritárias para conservação; realização de atividades de prevenção e combate _x000D_
-a incêndios e regularização fundiária das unidades de conservação.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revitalização aquática da Bacia Hidrográfica do Rio Doce, a partir do mapeamento _x000D_
-de áreas estratégicas para revitalização e conservação da fauna e flora aquáticas, em _x000D_
-especial áreas de cabeceiras, tributários e rotas de piracema, e execução de ações _x000D_
-como zoneamento pesqueiro; desassoreamento; reconformação de calhas de rios; _x000D_
-renaturalização de leitos de rios; reintrodução de espécies aquáticas ameaçadas; _x000D_
-educação ambiental, dentre outras ações baseadas na natureza para a revitalização _x000D_
-intracalha do Rio Doce e seus tributários._x000D_
-</t>
-  </si>
-  <si>
-    <t>Aquisição de materiais, equipamentos e capacitações para modernização das _x000D_
-estruturas de fiscalização ambiental e serviços de inteligência em fiscalização da _x000D_
-Secretaria Estadual do Meio Ambiente de Minas Gerais na Bacia Hidrográfica do Rio _x000D_
-Doce.</t>
-  </si>
-  <si>
     <t>Atualização e realização de novos estudos de Zoneamento Ambiental Produtivo em sub-bacias hidrográficas da bacia do rio Doce.</t>
   </si>
   <si>
     <t>Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho.</t>
   </si>
   <si>
-    <t>Oferta de capacitações continuadas em gestão para os profissionais do Sistema _x000D_
-Único da Assistência Social (SUAS), além do apoio na elaboração e execução do _x000D_
-Plano Municipal de Assistência Social.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e _x000D_
-PCMG) no Município de Mariana/MG.</t>
-  </si>
-  <si>
-    <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à _x000D_
-implementação das iniciativas.</t>
-  </si>
-  <si>
     <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas ambientais.</t>
   </si>
   <si>
@@ -157,24 +103,6 @@
     <t>Adequação de infraestrutura em áreas rurais.</t>
   </si>
   <si>
-    <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às _x000D_
-organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e _x000D_
-serviços, apoio na comunicação e marketing, mapeamento de necessidades de _x000D_
-infraestrutura e fornecimento de equipamentos e insumos.</t>
-  </si>
-  <si>
-    <t>Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica _x000D_
-e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a _x000D_
-capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a _x000D_
-recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de _x000D_
-eventos climáticos extremos.</t>
-  </si>
-  <si>
-    <t>Desenvolvimento e manutenção de sistemas de tecnologia e informação do _x000D_
-Sistema Estadual do Meio Ambiente (SISEMA) de forma a apoiar os investimentos _x000D_
-ambientais na Bacia Hidrográfica do Rio Doce.</t>
-  </si>
-  <si>
     <t>Melhoria na capacidade estadual fiscalizatória de barragens nas estruturas localizadas na extensão territorial da Bacia Hidrográfica do Rio Doce: aquisição de equipamentos físicos e tecnológicos, contratação de serviços de consultoria.</t>
   </si>
   <si>
@@ -202,35 +130,62 @@
     <t xml:space="preserve">Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais. </t>
   </si>
   <si>
-    <t>Criação de fundo de disponibilização de crédito para recuperação econômica de _x000D_
-pequenas, médias e grandes empresas dos municípios atingidos, além de fundo _x000D_
-garantidor para facilitar o acesso a essa linha de crédito.</t>
-  </si>
-  <si>
-    <t>Desenvolvimento e implantação de soluções técnicas para desafios de _x000D_
-conservação da biodiversidade da Bacia Hidrográfica do Rio Doce, como _x000D_
-monitoramento e reintrodução de espécies-alvo/ameaçadas, conservação em _x000D_
-cativeiro e reintrodução de espécies, dentre outras possíveis soluções.</t>
-  </si>
-  <si>
     <t>Reforma, modernização, equipagem e melhorias logísticas das estruturas físicas e dos serviços da Administração Pública - DENTRO DA BACIA</t>
   </si>
   <si>
-    <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da _x000D_
-infraestrutura viária - FORA DA BACIA.</t>
-  </si>
-  <si>
-    <t>Total Geral</t>
+    <t>Fortalecimento do atendimento da rede socioassistencial com execução de um _x000D_plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do Centro de Referência de Assistência Social (CRAS) e Centro de Referência _x000D_Especializado de Assistência Social (CREAS), contratação de equipe técnica e _x000D_aquisição de material de consumo de acordo com detalhamento a ser construído _x000D_prioritariamente.</t>
+  </si>
+  <si>
+    <t>Fortalecimento da política pública de gestão do manejo da fauna silvestre, de _x000D_acordo com mapeamento de necessidades a ser detalhado, a partir de ações como _x000D_da estruturação e custeio dos serviços prestados pelos Centros de Triagem e Reabilitação de Animais Silvestres (Cetas) que atendam à Bacia Hidrográfica do Rio Doce; contratação de serviços veterinários  especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da fauna.</t>
+  </si>
+  <si>
+    <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio _x000D_Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de _x000D_acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) _x000D_de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de _x000D_áreas prioritárias para conservação; realização de atividades de prevenção e combate _x000D_a incêndios e regularização fundiária das unidades de conservação.</t>
+  </si>
+  <si>
+    <t>Revitalização aquática da Bacia Hidrográfica do Rio Doce, a partir do mapeamento _x000D_de áreas estratégicas para revitalização e conservação da fauna e flora aquáticas, em _x000D_especial áreas de cabeceiras, tributários e rotas de piracema, e execução de ações _x000D_como zoneamento pesqueiro; desassoreamento; reconformação de calhas de rios; _x000D_renaturalização de leitos de rios; reintrodução de espécies aquáticas ameaçadas; _x000D_educação ambiental, dentre outras ações baseadas na natureza para a revitalização _x000D_intracalha do Rio Doce e seus tributários._x000D_</t>
+  </si>
+  <si>
+    <t>Aquisição de materiais, equipamentos e capacitações para modernização das _x000D_estruturas de fiscalização ambiental e serviços de inteligência em fiscalização da _x000D_Secretaria Estadual do Meio Ambiente de Minas Gerais na Bacia Hidrográfica do Rio _x000D_Doce.</t>
+  </si>
+  <si>
+    <t>Oferta de capacitações continuadas em gestão para os profissionais do Sistema _x000D_Único da Assistência Social (SUAS), além do apoio na elaboração e execução do _x000D_Plano Municipal de Assistência Social.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e _x000D_PCMG) no Município de Mariana/MG.</t>
+  </si>
+  <si>
+    <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à _x000D_implementação das iniciativas.</t>
+  </si>
+  <si>
+    <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às _x000D_organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e _x000D_serviços, apoio na comunicação e marketing, mapeamento de necessidades de _x000D_infraestrutura e fornecimento de equipamentos e insumos.</t>
+  </si>
+  <si>
+    <t>Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica _x000D_e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a _x000D_capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a _x000D_recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de _x000D_eventos climáticos extremos.</t>
+  </si>
+  <si>
+    <t>Desenvolvimento e manutenção de sistemas de tecnologia e informação do _x000D_Sistema Estadual do Meio Ambiente (SISEMA) de forma a apoiar os investimentos _x000D_ambientais na Bacia Hidrográfica do Rio Doce.</t>
+  </si>
+  <si>
+    <t>Criação de fundo de disponibilização de crédito para recuperação econômica de _x000D_pequenas, médias e grandes empresas dos municípios atingidos, além de fundo _x000D_garantidor para facilitar o acesso a essa linha de crédito.</t>
+  </si>
+  <si>
+    <t>Desenvolvimento e implantação de soluções técnicas para desafios de _x000D_conservação da biodiversidade da Bacia Hidrográfica do Rio Doce, como _x000D_monitoramento e reintrodução de espécies-alvo/ameaçadas, conservação em _x000D_cativeiro e reintrodução de espécies, dentre outras possíveis soluções.</t>
+  </si>
+  <si>
+    <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da _x000D_infraestrutura viária - FORA DA BACIA.</t>
+  </si>
+  <si>
+    <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da _x000D_infraestrutura viária.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -547,7 +502,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -720,24 +675,19 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
+      <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
@@ -755,7 +705,7 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color rgb="FF000000"/>
       </right>
       <top style="medium">
@@ -767,13 +717,28 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
@@ -791,7 +756,7 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -800,55 +765,10 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
@@ -914,7 +834,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -932,47 +852,38 @@
     <xf numFmtId="164" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1006,10 +917,10 @@
     <cellStyle name="Ênfase5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Ênfase6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Neutro" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Incorreto" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Neutra" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Nota" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Ruim" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Saída" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Texto de Aviso" xfId="14" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Texto Explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
@@ -1329,17 +1240,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
     <col min="2" max="2" width="76.28515625" customWidth="1"/>
     <col min="3" max="3" width="8.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" style="16" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30.75">
+    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1353,565 +1264,532 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="17">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
         <v>9445683</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="10">
         <v>220162500</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="18">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="16">
         <v>9445703</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="12">
         <v>100000000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="91.5">
-      <c r="A4" s="18">
+    <row r="4" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="16">
         <v>9445718</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="12">
+        <v>280999999.9955892</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="16">
+        <v>9445719</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="14">
-        <v>280999999.9955892</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="18">
-        <v>9445719</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="12">
+        <v>1026817301.85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="16">
+        <v>9445721</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="14">
-        <v>1026817301.85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="18">
-        <v>9445721</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="D6" s="12">
+        <v>250000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="16">
+        <v>9445763</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="14">
-        <v>250000000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="18">
-        <v>9445763</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="D7" s="12">
+        <v>1702476148.74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="16">
+        <v>9452379</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="12">
+        <v>466173769.14999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A9" s="16">
+        <v>9456605</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="12">
+        <v>19501138.120000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="16">
+        <v>9456606</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="12">
+        <v>781013478.41999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A11" s="16">
+        <v>9456612</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="12">
+        <v>447461489.31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="16">
+        <v>9456614</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="12">
+        <v>23690592.440000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="16">
+        <v>9456616</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="14">
-        <v>1702476148.74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="30.75">
-      <c r="A8" s="18">
-        <v>9452379</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="C13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="12">
+        <v>9500000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="16">
+        <v>9456621</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="14">
-        <v>466173769.14999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="91.5">
-      <c r="A9" s="18">
-        <v>9456605</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="C14" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="12">
+        <v>30351000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="16">
+        <v>9456622</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="12">
+        <v>53999999.996188097</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>9456627</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="12">
+        <v>20044942.060000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="16">
+        <v>9468055</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="12">
+        <v>215762851.11000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="16">
+        <v>9468057</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="14">
-        <v>19501138.120000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="91.5">
-      <c r="A10" s="18">
-        <v>9456606</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="C18" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="12">
+        <v>269884659.19999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="16">
+        <v>9470658</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="14">
-        <v>781013478.41999996</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="121.5">
-      <c r="A11" s="18">
-        <v>9456612</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="C19" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="12">
+        <v>3629681.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="16">
+        <v>9473170</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="14">
-        <v>447461489.31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="60.75">
-      <c r="A12" s="18">
-        <v>9456614</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="C20" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="12">
+        <v>3426230.8499999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="16">
+        <v>9473171</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="14">
-        <v>23690592.440000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="18">
-        <v>9456616</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="C21" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="12">
+        <v>78000000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="16">
+        <v>9474703</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="14">
-        <v>9500000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="18">
-        <v>9456621</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="C22" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="12">
+        <v>90000000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="16">
+        <v>9480259</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="12">
+        <v>55000000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A24" s="16">
+        <v>9480440</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="12">
+        <v>150000000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="16">
+        <v>9480692</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="12">
+        <v>33000000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="16">
+        <v>9480693</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="14">
-        <v>30351000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="45.75">
-      <c r="A15" s="18">
-        <v>9456622</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="C26" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="12">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="16">
+        <v>9484149</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="14">
-        <v>53999999.996188097</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="30.75">
-      <c r="A16" s="18">
-        <v>9456627</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="C27" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="12">
+        <v>21000000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="16">
+        <v>9484152</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="14">
-        <v>20044942.060000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="30.75">
-      <c r="A17" s="18">
-        <v>9468055</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="C28" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="12">
+        <v>3500000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="16">
+        <v>9484158</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="14">
-        <v>215762851.11000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="18">
-        <v>9468057</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="C29" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="12">
+        <v>2048623.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="16">
+        <v>9484244</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="14">
-        <v>269884659.19999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="18">
-        <v>9470658</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="C30" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="12">
+        <v>10716558.779999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="16">
+        <v>9493230</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="14">
-        <v>3629681.6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="18">
-        <v>9473170</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="C31" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="12">
+        <v>12291807.84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="16">
+        <v>9493391</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="14">
-        <v>3426230.8499999996</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="18">
-        <v>9473171</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="C32" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="12">
+        <v>16609578.82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="16">
+        <v>9494511</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="14">
-        <v>78000000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="18">
-        <v>9474703</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="C33" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="12">
+        <v>42400000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="16">
+        <v>9498925</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="14">
-        <v>90000000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="60.75">
-      <c r="A23" s="18">
-        <v>9480259</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="14">
-        <v>55000000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="76.5">
-      <c r="A24" s="18">
-        <v>9480440</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="14">
-        <v>150000000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="45.75">
-      <c r="A25" s="18">
-        <v>9480692</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="14">
-        <v>33000000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="18">
-        <v>9480693</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="14">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="18">
-        <v>9484149</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="14">
-        <v>21000000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="18">
-        <v>9484152</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="14">
-        <v>3500000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="18">
-        <v>9484158</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="14">
-        <v>2048623.4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="18">
-        <v>9484244</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="14">
-        <v>10716558.779999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="18">
-        <v>9493230</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="14">
-        <v>12291807.84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="18">
-        <v>9493391</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="14">
-        <v>16609578.82</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="18">
-        <v>9494511</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="14">
-        <v>42400000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="18">
-        <v>9498925</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="14">
+      <c r="C34" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="12">
         <v>124000000</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="45.75">
-      <c r="A35" s="18">
+    <row r="35" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A35" s="16">
         <v>9498928</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="14">
+      <c r="C35" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="12">
         <v>350000000</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="60.75">
-      <c r="A36" s="18">
+    <row r="36" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A36" s="16">
         <v>9499189</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="14">
+      <c r="C36" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="12">
         <v>53537119.670000002</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="18">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="16">
         <v>9501886</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="12">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="17">
+        <v>9501917</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="14">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="30.75">
-      <c r="A38" s="19">
-        <v>9501917</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="21">
+      <c r="C38" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="18">
         <v>7500000</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="20">
-        <v>6984499471.3517771</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <mergeCells count="1">
-    <mergeCell ref="A39:C39"/>
-  </mergeCells>
+  <autoFilter ref="A1:D1"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2d423e06-9c1f-4758-88fb-e70a58c28cf9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cc9e11e8-bdfc-4391-b4a2-bd31043e0387" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100ACDB477B8BFCDA4F8705659FCECBCBD8" ma:contentTypeVersion="16" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="16eb12ad33a5809568bcc6af6d82ddd1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2d423e06-9c1f-4758-88fb-e70a58c28cf9" xmlns:ns3="cc9e11e8-bdfc-4391-b4a2-bd31043e0387" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de2d0f1e826869e46cf6cda92c3d6a8e" ns2:_="" ns3:_="">
     <xsd:import namespace="2d423e06-9c1f-4758-88fb-e70a58c28cf9"/>
@@ -2152,14 +2030,60 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2d423e06-9c1f-4758-88fb-e70a58c28cf9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cc9e11e8-bdfc-4391-b4a2-bd31043e0387" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F562116-17A9-4E16-B96F-E16E691393B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBAB8ADE-93FF-4660-8C47-8AF7E93ACE7D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2d423e06-9c1f-4758-88fb-e70a58c28cf9"/>
+    <ds:schemaRef ds:uri="cc9e11e8-bdfc-4391-b4a2-bd31043e0387"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{642F9938-99F5-403F-8A78-110D7921267C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{642F9938-99F5-403F-8A78-110D7921267C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2d423e06-9c1f-4758-88fb-e70a58c28cf9"/>
+    <ds:schemaRef ds:uri="cc9e11e8-bdfc-4391-b4a2-bd31043e0387"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBAB8ADE-93FF-4660-8C47-8AF7E93ACE7D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F562116-17A9-4E16-B96F-E16E691393B4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/upload/iniciativa.xlsx
+++ b/upload/iniciativa.xlsx
@@ -139,43 +139,43 @@
     <t>Fortalecimento da política pública de gestão do manejo da fauna silvestre, de _x000D_acordo com mapeamento de necessidades a ser detalhado, a partir de ações como _x000D_da estruturação e custeio dos serviços prestados pelos Centros de Triagem e Reabilitação de Animais Silvestres (Cetas) que atendam à Bacia Hidrográfica do Rio Doce; contratação de serviços veterinários  especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da fauna.</t>
   </si>
   <si>
-    <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio _x000D_Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de _x000D_acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) _x000D_de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de _x000D_áreas prioritárias para conservação; realização de atividades de prevenção e combate _x000D_a incêndios e regularização fundiária das unidades de conservação.</t>
-  </si>
-  <si>
     <t>Revitalização aquática da Bacia Hidrográfica do Rio Doce, a partir do mapeamento _x000D_de áreas estratégicas para revitalização e conservação da fauna e flora aquáticas, em _x000D_especial áreas de cabeceiras, tributários e rotas de piracema, e execução de ações _x000D_como zoneamento pesqueiro; desassoreamento; reconformação de calhas de rios; _x000D_renaturalização de leitos de rios; reintrodução de espécies aquáticas ameaçadas; _x000D_educação ambiental, dentre outras ações baseadas na natureza para a revitalização _x000D_intracalha do Rio Doce e seus tributários._x000D_</t>
   </si>
   <si>
-    <t>Aquisição de materiais, equipamentos e capacitações para modernização das _x000D_estruturas de fiscalização ambiental e serviços de inteligência em fiscalização da _x000D_Secretaria Estadual do Meio Ambiente de Minas Gerais na Bacia Hidrográfica do Rio _x000D_Doce.</t>
-  </si>
-  <si>
-    <t>Oferta de capacitações continuadas em gestão para os profissionais do Sistema _x000D_Único da Assistência Social (SUAS), além do apoio na elaboração e execução do _x000D_Plano Municipal de Assistência Social.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e _x000D_PCMG) no Município de Mariana/MG.</t>
-  </si>
-  <si>
-    <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à _x000D_implementação das iniciativas.</t>
-  </si>
-  <si>
-    <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às _x000D_organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e _x000D_serviços, apoio na comunicação e marketing, mapeamento de necessidades de _x000D_infraestrutura e fornecimento de equipamentos e insumos.</t>
-  </si>
-  <si>
-    <t>Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica _x000D_e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a _x000D_capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a _x000D_recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de _x000D_eventos climáticos extremos.</t>
-  </si>
-  <si>
-    <t>Desenvolvimento e manutenção de sistemas de tecnologia e informação do _x000D_Sistema Estadual do Meio Ambiente (SISEMA) de forma a apoiar os investimentos _x000D_ambientais na Bacia Hidrográfica do Rio Doce.</t>
-  </si>
-  <si>
-    <t>Criação de fundo de disponibilização de crédito para recuperação econômica de _x000D_pequenas, médias e grandes empresas dos municípios atingidos, além de fundo _x000D_garantidor para facilitar o acesso a essa linha de crédito.</t>
-  </si>
-  <si>
-    <t>Desenvolvimento e implantação de soluções técnicas para desafios de _x000D_conservação da biodiversidade da Bacia Hidrográfica do Rio Doce, como _x000D_monitoramento e reintrodução de espécies-alvo/ameaçadas, conservação em _x000D_cativeiro e reintrodução de espécies, dentre outras possíveis soluções.</t>
-  </si>
-  <si>
-    <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da _x000D_infraestrutura viária - FORA DA BACIA.</t>
-  </si>
-  <si>
     <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da _x000D_infraestrutura viária.</t>
+  </si>
+  <si>
+    <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de _x000D_acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) _x000D_de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de _x000D_áreas prioritárias para conservação; realização de atividades de prevenção e combate _x000D_a incêndios e regularização fundiária das unidades de conservação.</t>
+  </si>
+  <si>
+    <t>Aquisição de materiais, equipamentos e capacitações para modernização das estruturas de fiscalização ambiental e serviços de inteligência em fiscalização da _x000D_Secretaria Estadual do Meio Ambiente de Minas Gerais na Bacia Hidrográfica do Rio _x000D_Doce.</t>
+  </si>
+  <si>
+    <t>Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e _x000D_PCMG) no Município de Mariana/MG.</t>
+  </si>
+  <si>
+    <t>Oferta de capacitações continuadas em gestão para os profissionais do Sistema Único da Assistência Social (SUAS), além do apoio na elaboração e execução do _x000D_Plano Municipal de Assistência Social.</t>
+  </si>
+  <si>
+    <t>Suporte gerencial, administrativo, tecnológico e de comhnicação social à implementação das iniciativas.</t>
+  </si>
+  <si>
+    <t>Fomento ao associativismo e ao cooperativismo a partir de assessorias às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e _x000D_serviços, apoio na comunicação e marketing, mapeamento de necessidades de _x000D_infraestrutura e fornecimento de equipamentos e insumos.</t>
+  </si>
+  <si>
+    <t>Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a _x000D_capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a _x000D_recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de _x000D_eventos climáticos extremos.</t>
+  </si>
+  <si>
+    <t>Desenvolvimento e manutenção de sistemas de tecnologia e informação do Sistema Estadual do Meio Ambiente (SISEMA) de forma a apoiar os investimentos ambientais na Bacia Hidrográfica do Rio Doce.</t>
+  </si>
+  <si>
+    <t>Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo _x000D_garantidor para facilitar o acesso a essa linha de crédito.</t>
+  </si>
+  <si>
+    <t>Desenvolvimento e implantação de soluções técnicas para desafios de conservação da biodiversidade da Bacia Hidrográfica do Rio Doce, como _x000D_monitoramento e reintrodução de espécies-alvo/ameaçadas, conservação em _x000D_cativeiro e reintrodução de espécies, dentre outras possíveis soluções.</t>
+  </si>
+  <si>
+    <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária - FORA DA BACIA.</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1245,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
-    <col min="2" max="2" width="76.28515625" customWidth="1"/>
+    <col min="2" max="2" width="234.42578125" customWidth="1"/>
     <col min="3" max="3" width="8.85546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="26.5703125" style="14" customWidth="1"/>
   </cols>
@@ -1292,7 +1292,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <v>9445718</v>
       </c>
@@ -1348,12 +1348,12 @@
         <v>1702476148.74</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>9452379</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>8</v>
@@ -1362,7 +1362,7 @@
         <v>466173769.14999998</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>9456605</v>
       </c>
@@ -1376,12 +1376,12 @@
         <v>19501138.120000001</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <v>9456606</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>8</v>
@@ -1390,12 +1390,12 @@
         <v>781013478.41999996</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>9456612</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>8</v>
@@ -1404,12 +1404,12 @@
         <v>447461489.31</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>9456614</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>8</v>
@@ -1446,12 +1446,12 @@
         <v>30351000</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>9456622</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>8</v>
@@ -1460,7 +1460,7 @@
         <v>53999999.996188097</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <v>9456627</v>
       </c>
@@ -1474,12 +1474,12 @@
         <v>20044942.060000002</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>9468055</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>8</v>
@@ -1558,12 +1558,12 @@
         <v>90000000</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>9480259</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>8</v>
@@ -1572,12 +1572,12 @@
         <v>55000000</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <v>9480440</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>8</v>
@@ -1586,12 +1586,12 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>9480692</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>8</v>
@@ -1726,12 +1726,12 @@
         <v>124000000</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>9498928</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>8</v>
@@ -1740,12 +1740,12 @@
         <v>350000000</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <v>9499189</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>8</v>
@@ -1768,12 +1768,12 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="17">
         <v>9501917</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>8</v>
@@ -1790,6 +1790,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2d423e06-9c1f-4758-88fb-e70a58c28cf9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cc9e11e8-bdfc-4391-b4a2-bd31043e0387" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100ACDB477B8BFCDA4F8705659FCECBCBD8" ma:contentTypeVersion="16" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="16eb12ad33a5809568bcc6af6d82ddd1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2d423e06-9c1f-4758-88fb-e70a58c28cf9" xmlns:ns3="cc9e11e8-bdfc-4391-b4a2-bd31043e0387" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de2d0f1e826869e46cf6cda92c3d6a8e" ns2:_="" ns3:_="">
     <xsd:import namespace="2d423e06-9c1f-4758-88fb-e70a58c28cf9"/>
@@ -2030,27 +2050,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2d423e06-9c1f-4758-88fb-e70a58c28cf9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cc9e11e8-bdfc-4391-b4a2-bd31043e0387" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F562116-17A9-4E16-B96F-E16E691393B4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{642F9938-99F5-403F-8A78-110D7921267C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2d423e06-9c1f-4758-88fb-e70a58c28cf9"/>
+    <ds:schemaRef ds:uri="cc9e11e8-bdfc-4391-b4a2-bd31043e0387"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBAB8ADE-93FF-4660-8C47-8AF7E93ACE7D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2067,23 +2086,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{642F9938-99F5-403F-8A78-110D7921267C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2d423e06-9c1f-4758-88fb-e70a58c28cf9"/>
-    <ds:schemaRef ds:uri="cc9e11e8-bdfc-4391-b4a2-bd31043e0387"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F562116-17A9-4E16-B96F-E16E691393B4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/upload/iniciativa.xlsx
+++ b/upload/iniciativa.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30318"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x6557308\Desktop\Trabalho\CGE - Transparência RD\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{191BDAB3-E908-4168-93B2-72D6C933D104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portal Transparência - CGE" sheetId="4" r:id="rId1"/>
@@ -17,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portal Transparência - CGE'!$A$1:$D$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="51">
   <si>
     <t>Código Iniciativa </t>
   </si>
@@ -52,6 +53,12 @@
     <t>Valor da Iniciativa </t>
   </si>
   <si>
+    <t>Fortalecimento do SUAS ESTADUAL</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
     <t>Plano de Ação em Saúde do Rio Doce</t>
   </si>
   <si>
@@ -64,6 +71,10 @@
     <t>X</t>
   </si>
   <si>
+    <t>Fortalecimento do atendimento da rede socioassistencial com execução de um plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do Centro de Referência de Assistência Social (CRAS) e Centro de Referência 
+Especializado de Assistência Social (CREAS), contratação de equipe técnica e aquisição de material de consumo de acordo com detalhamento a ser construído prioritariamente.</t>
+  </si>
+  <si>
     <t>XII</t>
   </si>
   <si>
@@ -82,12 +93,37 @@
     <t>XIII</t>
   </si>
   <si>
+    <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária.</t>
+  </si>
+  <si>
+    <t>Fortalecimento da política pública de gestão do manejo da fauna silvestre, de acordo com mapeamento de necessidades a ser detalhado, a partir de ações como da estruturação e custeio dos serviços prestados pelos Centros de Triagem e Reabilitação de Animais Silvestres (Cetas) que atendam à Bacia Hidrográfica do Rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da fauna.</t>
+  </si>
+  <si>
+    <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de  acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s)  de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revitalização aquática da Bacia Hidrográfica do Rio Doce, a partir do mapeamento de áreas estratégicas para revitalização e conservação da fauna e flora aquáticas, em especial áreas de cabeceiras, tributários e rotas de piracema, e execução de ações como zoneamento pesqueiro; desassoreamento; reconformação de calhas de rios; renaturalização de leitos de rios; reintrodução de espécies aquáticas ameaçadas; educação ambiental, dentre outras ações baseadas na natureza para a revitalização intracalha do Rio Doce e seus tributários.
+</t>
+  </si>
+  <si>
+    <t>Aquisição de materiais, equipamentos e capacitações para modernização das estruturas de fiscalização ambiental e serviços de inteligência em fiscalização da  Secretaria Estadual do Meio Ambiente de Minas Gerais na Bacia Hidrográfica do Rio Doce.</t>
+  </si>
+  <si>
     <t>Atualização e realização de novos estudos de Zoneamento Ambiental Produtivo em sub-bacias hidrográficas da bacia do rio Doce.</t>
   </si>
   <si>
     <t>Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho.</t>
   </si>
   <si>
+    <t>Oferta de capacitações continuadas em gestão para os profissionais do Sistema Único da Assistência Social (SUAS), além do apoio na elaboração e execução do Plano Municipal de Assistência Social.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e PCMG) no Município de Mariana/MG.</t>
+  </si>
+  <si>
+    <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas.</t>
+  </si>
+  <si>
     <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas ambientais.</t>
   </si>
   <si>
@@ -103,6 +139,15 @@
     <t>Adequação de infraestrutura em áreas rurais.</t>
   </si>
   <si>
+    <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos.</t>
+  </si>
+  <si>
+    <t>Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+  </si>
+  <si>
+    <t>Desenvolvimento e manutenção de sistemas de tecnologia e informação do Sistema Estadual do Meio Ambiente (SISEMA) de forma a apoiar os investimentos ambientais na Bacia Hidrográfica do Rio Doce.</t>
+  </si>
+  <si>
     <t>Melhoria na capacidade estadual fiscalizatória de barragens nas estruturas localizadas na extensão territorial da Bacia Hidrográfica do Rio Doce: aquisição de equipamentos físicos e tecnológicos, contratação de serviços de consultoria.</t>
   </si>
   <si>
@@ -130,62 +175,35 @@
     <t xml:space="preserve">Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais. </t>
   </si>
   <si>
+    <t>Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito.</t>
+  </si>
+  <si>
+    <t>Desenvolvimento e implantação de soluções técnicas para desafios de conservação da biodiversidade da Bacia Hidrográfica do Rio Doce, como monitoramento e reintrodução de espécies-alvo/ameaçadas, conservação em cativeiro e reintrodução de espécies, dentre outras possíveis soluções.</t>
+  </si>
+  <si>
     <t>Reforma, modernização, equipagem e melhorias logísticas das estruturas físicas e dos serviços da Administração Pública - DENTRO DA BACIA</t>
   </si>
   <si>
-    <t>Fortalecimento do atendimento da rede socioassistencial com execução de um _x000D_plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do Centro de Referência de Assistência Social (CRAS) e Centro de Referência _x000D_Especializado de Assistência Social (CREAS), contratação de equipe técnica e _x000D_aquisição de material de consumo de acordo com detalhamento a ser construído _x000D_prioritariamente.</t>
-  </si>
-  <si>
-    <t>Fortalecimento da política pública de gestão do manejo da fauna silvestre, de _x000D_acordo com mapeamento de necessidades a ser detalhado, a partir de ações como _x000D_da estruturação e custeio dos serviços prestados pelos Centros de Triagem e Reabilitação de Animais Silvestres (Cetas) que atendam à Bacia Hidrográfica do Rio Doce; contratação de serviços veterinários  especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da fauna.</t>
-  </si>
-  <si>
-    <t>Revitalização aquática da Bacia Hidrográfica do Rio Doce, a partir do mapeamento _x000D_de áreas estratégicas para revitalização e conservação da fauna e flora aquáticas, em _x000D_especial áreas de cabeceiras, tributários e rotas de piracema, e execução de ações _x000D_como zoneamento pesqueiro; desassoreamento; reconformação de calhas de rios; _x000D_renaturalização de leitos de rios; reintrodução de espécies aquáticas ameaçadas; _x000D_educação ambiental, dentre outras ações baseadas na natureza para a revitalização _x000D_intracalha do Rio Doce e seus tributários._x000D_</t>
-  </si>
-  <si>
-    <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da _x000D_infraestrutura viária.</t>
-  </si>
-  <si>
-    <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de _x000D_acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) _x000D_de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de _x000D_áreas prioritárias para conservação; realização de atividades de prevenção e combate _x000D_a incêndios e regularização fundiária das unidades de conservação.</t>
-  </si>
-  <si>
-    <t>Aquisição de materiais, equipamentos e capacitações para modernização das estruturas de fiscalização ambiental e serviços de inteligência em fiscalização da _x000D_Secretaria Estadual do Meio Ambiente de Minas Gerais na Bacia Hidrográfica do Rio _x000D_Doce.</t>
-  </si>
-  <si>
-    <t>Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e _x000D_PCMG) no Município de Mariana/MG.</t>
-  </si>
-  <si>
-    <t>Oferta de capacitações continuadas em gestão para os profissionais do Sistema Único da Assistência Social (SUAS), além do apoio na elaboração e execução do _x000D_Plano Municipal de Assistência Social.</t>
-  </si>
-  <si>
-    <t>Suporte gerencial, administrativo, tecnológico e de comhnicação social à implementação das iniciativas.</t>
-  </si>
-  <si>
-    <t>Fomento ao associativismo e ao cooperativismo a partir de assessorias às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e _x000D_serviços, apoio na comunicação e marketing, mapeamento de necessidades de _x000D_infraestrutura e fornecimento de equipamentos e insumos.</t>
-  </si>
-  <si>
-    <t>Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a _x000D_capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a _x000D_recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de _x000D_eventos climáticos extremos.</t>
-  </si>
-  <si>
-    <t>Desenvolvimento e manutenção de sistemas de tecnologia e informação do Sistema Estadual do Meio Ambiente (SISEMA) de forma a apoiar os investimentos ambientais na Bacia Hidrográfica do Rio Doce.</t>
-  </si>
-  <si>
-    <t>Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo _x000D_garantidor para facilitar o acesso a essa linha de crédito.</t>
-  </si>
-  <si>
-    <t>Desenvolvimento e implantação de soluções técnicas para desafios de conservação da biodiversidade da Bacia Hidrográfica do Rio Doce, como _x000D_monitoramento e reintrodução de espécies-alvo/ameaçadas, conservação em _x000D_cativeiro e reintrodução de espécies, dentre outras possíveis soluções.</t>
-  </si>
-  <si>
     <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária - FORA DA BACIA.</t>
+  </si>
+  <si>
+    <t>Gestão do recurso pesqueiro na Bacia do Rio Doce</t>
+  </si>
+  <si>
+    <t>Reconstrução de Pontes de Ubá</t>
+  </si>
+  <si>
+    <t>Total Geral</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -502,7 +520,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -750,25 +768,75 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
@@ -777,10 +845,34 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
@@ -834,15 +926,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -852,39 +940,68 @@
     <xf numFmtId="164" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -917,10 +1034,10 @@
     <cellStyle name="Ênfase5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Ênfase6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Incorreto" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Neutra" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Neutro" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Nota" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Ruim" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Saída" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Texto de Aviso" xfId="14" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Texto Explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
@@ -931,7 +1048,18 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1240,550 +1368,609 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D42"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
-    <col min="2" max="2" width="234.42578125" customWidth="1"/>
+    <col min="2" max="2" width="76.28515625" customWidth="1"/>
     <col min="3" max="3" width="8.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" style="14" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" ht="30.75">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
-        <v>9445683</v>
+    <row r="2" spans="1:4">
+      <c r="A2" s="6">
+        <v>9445684</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
+        <v>32000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="10">
+        <v>9445683</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="13">
         <v>220162500</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="16">
+    <row r="4" spans="1:4">
+      <c r="A4" s="14">
         <v>9445703</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="12">
+      <c r="B4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="17">
         <v>100000000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="16">
+    <row r="5" spans="1:4" ht="91.5">
+      <c r="A5" s="14">
         <v>9445718</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="17">
+        <v>280999999.9955892</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="14">
+        <v>9445719</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="17">
+        <v>1026817301.85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="14">
+        <v>9445721</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="17">
+        <v>250000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="14">
+        <v>9445763</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="17">
+        <v>1702476148.74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="30.75">
+      <c r="A9" s="14">
+        <v>9452379</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="17">
+        <v>576437029.10000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="91.5">
+      <c r="A10" s="14">
+        <v>9456605</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="17">
+        <v>19501138.120000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="91.5">
+      <c r="A11" s="14">
+        <v>9456606</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="17">
+        <v>781013478.41999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="121.5">
+      <c r="A12" s="14">
+        <v>9456612</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="17">
+        <v>447461489.31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="60.75">
+      <c r="A13" s="14">
+        <v>9456614</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="17">
+        <v>23690592.440000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="14">
+        <v>9456616</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="17">
+        <v>9500000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="14">
+        <v>9456621</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="17">
+        <v>30351000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="45.75">
+      <c r="A16" s="14">
+        <v>9456622</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="17">
+        <v>53999999.996188097</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="30.75">
+      <c r="A17" s="14">
+        <v>9456627</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="17">
+        <v>20044942.060000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="30.75">
+      <c r="A18" s="14">
+        <v>9468055</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="17">
+        <v>215762851.11000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="14">
+        <v>9468057</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="17">
+        <v>269884659.19999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="14">
+        <v>9470658</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="17">
+        <v>3629681.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="14">
+        <v>9473170</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="17">
+        <v>538743.04000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="14">
+        <v>9473171</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="17">
+        <v>78000000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="14">
+        <v>9474703</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="12">
-        <v>280999999.9955892</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
-        <v>9445719</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C23" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="17">
+        <v>90000000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="60.75">
+      <c r="A24" s="14">
+        <v>9480259</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="17">
+        <v>55000000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="60.75">
+      <c r="A25" s="14">
+        <v>9480440</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="17">
+        <v>150000000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="45.75">
+      <c r="A26" s="14">
+        <v>9480692</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="17">
+        <v>33000000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="14">
+        <v>9480693</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="17">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="14">
+        <v>9484149</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="12">
-        <v>1026817301.85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="16">
-        <v>9445721</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="12">
-        <v>250000000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="16">
-        <v>9445763</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="12">
-        <v>1702476148.74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="16">
-        <v>9452379</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="12">
-        <v>466173769.14999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="16">
-        <v>9456605</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="12">
-        <v>19501138.120000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="16">
-        <v>9456606</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="12">
-        <v>781013478.41999996</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="16">
-        <v>9456612</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="12">
-        <v>447461489.31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
-        <v>9456614</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="12">
-        <v>23690592.440000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="16">
-        <v>9456616</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="D28" s="17">
+        <v>21000000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="14">
+        <v>9484152</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="17">
+        <v>3500000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="14">
+        <v>9484158</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="17">
+        <v>2048623.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="14">
+        <v>9484244</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="17">
+        <v>10716558.779999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="14">
+        <v>9493230</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="12">
-        <v>9500000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="16">
-        <v>9456621</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="12">
-        <v>30351000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="16">
-        <v>9456622</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="12">
-        <v>53999999.996188097</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="16">
-        <v>9456627</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="12">
-        <v>20044942.060000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
-        <v>9468055</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="12">
-        <v>215762851.11000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
-        <v>9468057</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="12">
-        <v>269884659.19999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="16">
-        <v>9470658</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="12">
-        <v>3629681.6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="16">
-        <v>9473170</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="12">
-        <v>3426230.8499999996</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="16">
-        <v>9473171</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="12">
-        <v>78000000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
-        <v>9474703</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="12">
-        <v>90000000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="16">
-        <v>9480259</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="12">
-        <v>55000000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="16">
-        <v>9480440</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="D32" s="17">
+        <v>12291807.84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="14">
+        <v>9493391</v>
+      </c>
+      <c r="B33" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="12">
-        <v>150000000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="16">
-        <v>9480692</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="C33" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="17">
+        <v>16609578.82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="14">
+        <v>9494511</v>
+      </c>
+      <c r="B34" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="12">
-        <v>33000000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="16">
-        <v>9480693</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="12">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="16">
-        <v>9484149</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="12">
-        <v>21000000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="16">
-        <v>9484152</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="12">
-        <v>3500000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="16">
-        <v>9484158</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="12">
-        <v>2048623.4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="16">
-        <v>9484244</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="12">
-        <v>10716558.779999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="16">
-        <v>9493230</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="12">
-        <v>12291807.84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="16">
-        <v>9493391</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="12">
-        <v>16609578.82</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="16">
-        <v>9494511</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="12">
+      <c r="C34" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="17">
         <v>42400000</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="16">
+    <row r="35" spans="1:4">
+      <c r="A35" s="14">
         <v>9498925</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="12">
+      <c r="B35" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="17">
         <v>124000000</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="16">
+    <row r="36" spans="1:4" ht="45.75">
+      <c r="A36" s="14">
         <v>9498928</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="12">
+      <c r="B36" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="17">
         <v>350000000</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="16">
+    <row r="37" spans="1:4" ht="60.75">
+      <c r="A37" s="14">
         <v>9499189</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="12">
+      <c r="B37" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="17">
         <v>53537119.670000002</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="16">
+    <row r="38" spans="1:4">
+      <c r="A38" s="14">
         <v>9501886</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="12">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="17">
+      <c r="B38" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="17">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="30.75">
+      <c r="A39" s="14">
         <v>9501917</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="18">
+      <c r="B39" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="17">
         <v>7500000</v>
       </c>
     </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="14">
+        <v>9480691</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="17">
+        <v>49440463.630000003</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="19">
+        <v>9501912</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="22">
+        <v>48000000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="23">
+        <f>SUM(D2:D41)</f>
+        <v>7220315707.1217766</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A1:D42" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <mergeCells count="1">
+    <mergeCell ref="A42:C42"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1799,17 +1986,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2d423e06-9c1f-4758-88fb-e70a58c28cf9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cc9e11e8-bdfc-4391-b4a2-bd31043e0387" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100ACDB477B8BFCDA4F8705659FCECBCBD8" ma:contentTypeVersion="16" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="16eb12ad33a5809568bcc6af6d82ddd1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2d423e06-9c1f-4758-88fb-e70a58c28cf9" xmlns:ns3="cc9e11e8-bdfc-4391-b4a2-bd31043e0387" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de2d0f1e826869e46cf6cda92c3d6a8e" ns2:_="" ns3:_="">
     <xsd:import namespace="2d423e06-9c1f-4758-88fb-e70a58c28cf9"/>
@@ -2050,40 +2226,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2d423e06-9c1f-4758-88fb-e70a58c28cf9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cc9e11e8-bdfc-4391-b4a2-bd31043e0387" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F562116-17A9-4E16-B96F-E16E691393B4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F562116-17A9-4E16-B96F-E16E691393B4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{642F9938-99F5-403F-8A78-110D7921267C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2d423e06-9c1f-4758-88fb-e70a58c28cf9"/>
-    <ds:schemaRef ds:uri="cc9e11e8-bdfc-4391-b4a2-bd31043e0387"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBAB8ADE-93FF-4660-8C47-8AF7E93ACE7D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBAB8ADE-93FF-4660-8C47-8AF7E93ACE7D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2d423e06-9c1f-4758-88fb-e70a58c28cf9"/>
-    <ds:schemaRef ds:uri="cc9e11e8-bdfc-4391-b4a2-bd31043e0387"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{642F9938-99F5-403F-8A78-110D7921267C}"/>
 </file>
--- a/upload/iniciativa.xlsx
+++ b/upload/iniciativa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x6557308\Desktop\Trabalho\CGE - Transparência RD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{191BDAB3-E908-4168-93B2-72D6C933D104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5C280C-B67D-4086-AC04-821261A70253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19230" yWindow="0" windowWidth="19170" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portal Transparência - CGE" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="50">
   <si>
     <t>Código Iniciativa </t>
   </si>
@@ -191,9 +191,6 @@
   </si>
   <si>
     <t>Reconstrução de Pontes de Ubá</t>
-  </si>
-  <si>
-    <t>Total Geral</t>
   </si>
 </sst>
 </file>
@@ -203,7 +200,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -520,7 +517,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -765,21 +762,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -827,30 +809,6 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -926,7 +884,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -955,16 +913,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
@@ -982,25 +940,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1073,9 +1022,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1113,7 +1062,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1219,7 +1168,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1361,7 +1310,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1369,8 +1318,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
     <col min="2" max="2" width="76.28515625" customWidth="1"/>
@@ -1378,7 +1327,7 @@
     <col min="4" max="4" width="26.5703125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30.75">
+    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1392,7 +1341,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>9445684</v>
       </c>
@@ -1406,7 +1355,7 @@
         <v>32000000</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <v>9445683</v>
       </c>
@@ -1420,7 +1369,7 @@
         <v>220162500</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>9445703</v>
       </c>
@@ -1434,7 +1383,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="91.5">
+    <row r="5" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>9445718</v>
       </c>
@@ -1448,7 +1397,7 @@
         <v>280999999.9955892</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>9445719</v>
       </c>
@@ -1462,7 +1411,7 @@
         <v>1026817301.85</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>9445721</v>
       </c>
@@ -1476,7 +1425,7 @@
         <v>250000000</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>9445763</v>
       </c>
@@ -1490,7 +1439,7 @@
         <v>1702476148.74</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="30.75">
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>9452379</v>
       </c>
@@ -1504,7 +1453,7 @@
         <v>576437029.10000002</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="91.5">
+    <row r="10" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>9456605</v>
       </c>
@@ -1518,7 +1467,7 @@
         <v>19501138.120000001</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="91.5">
+    <row r="11" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>9456606</v>
       </c>
@@ -1532,7 +1481,7 @@
         <v>781013478.41999996</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="121.5">
+    <row r="12" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>9456612</v>
       </c>
@@ -1546,7 +1495,7 @@
         <v>447461489.31</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="60.75">
+    <row r="13" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>9456614</v>
       </c>
@@ -1560,7 +1509,7 @@
         <v>23690592.440000001</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>9456616</v>
       </c>
@@ -1574,7 +1523,7 @@
         <v>9500000</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>9456621</v>
       </c>
@@ -1588,7 +1537,7 @@
         <v>30351000</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="45.75">
+    <row r="16" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>9456622</v>
       </c>
@@ -1602,7 +1551,7 @@
         <v>53999999.996188097</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="30.75">
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>9456627</v>
       </c>
@@ -1616,7 +1565,7 @@
         <v>20044942.060000002</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="30.75">
+    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>9468055</v>
       </c>
@@ -1630,7 +1579,7 @@
         <v>215762851.11000001</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>9468057</v>
       </c>
@@ -1644,7 +1593,7 @@
         <v>269884659.19999999</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>9470658</v>
       </c>
@@ -1658,7 +1607,7 @@
         <v>3629681.6</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>9473170</v>
       </c>
@@ -1672,7 +1621,7 @@
         <v>538743.04000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>9473171</v>
       </c>
@@ -1686,7 +1635,7 @@
         <v>78000000</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>9474703</v>
       </c>
@@ -1700,7 +1649,7 @@
         <v>90000000</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="60.75">
+    <row r="24" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>9480259</v>
       </c>
@@ -1714,7 +1663,7 @@
         <v>55000000</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="60.75">
+    <row r="25" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>9480440</v>
       </c>
@@ -1728,7 +1677,7 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="45.75">
+    <row r="26" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>9480692</v>
       </c>
@@ -1742,7 +1691,7 @@
         <v>33000000</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>9480693</v>
       </c>
@@ -1756,7 +1705,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>9484149</v>
       </c>
@@ -1770,7 +1719,7 @@
         <v>21000000</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="14">
         <v>9484152</v>
       </c>
@@ -1784,7 +1733,7 @@
         <v>3500000</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="14">
         <v>9484158</v>
       </c>
@@ -1798,7 +1747,7 @@
         <v>2048623.4</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="14">
         <v>9484244</v>
       </c>
@@ -1812,7 +1761,7 @@
         <v>10716558.779999999</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="14">
         <v>9493230</v>
       </c>
@@ -1826,7 +1775,7 @@
         <v>12291807.84</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="14">
         <v>9493391</v>
       </c>
@@ -1840,7 +1789,7 @@
         <v>16609578.82</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="14">
         <v>9494511</v>
       </c>
@@ -1854,7 +1803,7 @@
         <v>42400000</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="14">
         <v>9498925</v>
       </c>
@@ -1868,7 +1817,7 @@
         <v>124000000</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="45.75">
+    <row r="36" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="14">
         <v>9498928</v>
       </c>
@@ -1882,7 +1831,7 @@
         <v>350000000</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="60.75">
+    <row r="37" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="14">
         <v>9499189</v>
       </c>
@@ -1896,7 +1845,7 @@
         <v>53537119.670000002</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="14">
         <v>9501886</v>
       </c>
@@ -1910,7 +1859,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="30.75">
+    <row r="39" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="14">
         <v>9501917</v>
       </c>
@@ -1924,7 +1873,7 @@
         <v>7500000</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="14">
         <v>9480691</v>
       </c>
@@ -1938,7 +1887,7 @@
         <v>49440463.630000003</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="19">
         <v>9501912</v>
       </c>
@@ -1952,22 +1901,8 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="23">
-        <f>SUM(D2:D41)</f>
-        <v>7220315707.1217766</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D42" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <mergeCells count="1">
-    <mergeCell ref="A42:C42"/>
-  </mergeCells>
+  <autoFilter ref="A1:D41" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
@@ -1977,15 +1912,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100ACDB477B8BFCDA4F8705659FCECBCBD8" ma:contentTypeVersion="16" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="16eb12ad33a5809568bcc6af6d82ddd1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2d423e06-9c1f-4758-88fb-e70a58c28cf9" xmlns:ns3="cc9e11e8-bdfc-4391-b4a2-bd31043e0387" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de2d0f1e826869e46cf6cda92c3d6a8e" ns2:_="" ns3:_="">
     <xsd:import namespace="2d423e06-9c1f-4758-88fb-e70a58c28cf9"/>
@@ -2226,6 +2152,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2238,13 +2173,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F562116-17A9-4E16-B96F-E16E691393B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBAB8ADE-93FF-4660-8C47-8AF7E93ACE7D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2d423e06-9c1f-4758-88fb-e70a58c28cf9"/>
+    <ds:schemaRef ds:uri="cc9e11e8-bdfc-4391-b4a2-bd31043e0387"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBAB8ADE-93FF-4660-8C47-8AF7E93ACE7D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F562116-17A9-4E16-B96F-E16E691393B4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{642F9938-99F5-403F-8A78-110D7921267C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{642F9938-99F5-403F-8A78-110D7921267C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2d423e06-9c1f-4758-88fb-e70a58c28cf9"/>
+    <ds:schemaRef ds:uri="cc9e11e8-bdfc-4391-b4a2-bd31043e0387"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>